--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DE9"/>
+  <dimension ref="A1:DE11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3360,9 +3360,667 @@
         <v>Correct</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>امتحان البرمجه - الدرس الاول - الدرس الثاني</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mahmoud Mostafa</v>
+      </c>
+      <c r="C10" t="str">
+        <v>01055686885</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-09-10T16:21:16.145Z</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-09-10T16:22:16.090Z</v>
+      </c>
+      <c r="F10" t="str">
+        <v>page-hidden</v>
+      </c>
+      <c r="G10" t="str">
+        <v>0/50</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <v>REVIEW</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="O10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="R10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="T10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="V10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AH10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AK10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AM10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AN10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AO10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AP10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AQ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AR10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AS10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AT10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AU10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AV10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AW10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AX10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AY10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AZ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BA10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BB10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BC10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BD10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BE10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BF10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BG10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BH10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BI10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BJ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BK10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BL10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BM10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BN10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BO10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BP10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BQ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BR10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BS10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BT10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BU10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BV10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BW10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BX10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BY10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BZ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CA10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CB10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CC10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CD10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CE10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CF10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CG10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CH10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CI10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CJ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CK10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CL10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CM10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CN10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CO10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CP10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CQ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CR10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CS10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CT10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CU10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CV10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CW10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CX10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CY10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CZ10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DA10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DB10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DC10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DD10" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DE10" t="str">
+        <v>Not answered</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>امتحان البرمجه - الدرس الاول - الدرس الثاني</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Mahmoud Mostafa 2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>01055686885</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-09-10T16:40:47.696Z</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-09-10T16:40:55.564Z</v>
+      </c>
+      <c r="F11" t="str">
+        <v>manual</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0/50</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v>REVIEW</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="R11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="S11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="T11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="V11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AG11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AH11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>D</v>
+      </c>
+      <c r="AM11" t="str">
+        <v>Wrong</v>
+      </c>
+      <c r="AN11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AO11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AP11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AQ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AR11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AS11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AT11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AU11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AV11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AW11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AX11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AY11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="AZ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BA11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BB11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BC11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BD11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BE11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BF11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BG11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BH11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BI11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BJ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BK11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BL11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BM11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BN11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BO11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BP11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BQ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BR11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BS11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BT11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BU11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BV11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BW11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BX11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BY11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="BZ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CA11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CB11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CC11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CD11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CE11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CF11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CG11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CH11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CI11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CJ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CK11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CL11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CM11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CN11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CO11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CP11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CQ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CR11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CS11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CT11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CU11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CV11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CW11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CX11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CY11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="CZ11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DA11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DB11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DC11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DD11" t="str">
+        <v>Not answered</v>
+      </c>
+      <c r="DE11" t="str">
+        <v>Not answered</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DE9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:DE11"/>
   </ignoredErrors>
 </worksheet>
 </file>